--- a/invoices/invoice_2026-01-09.xlsx
+++ b/invoices/invoice_2026-01-09.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>OVERDUE</t>
         </is>
       </c>
     </row>
